--- a/data/gravel/Lapierre Crosshill 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4248C8-AF77-2947-965D-B147AF888DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C82DF8-7DEF-2540-AF0F-D3043E43AF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33520" yWindow="-23280" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28100" yWindow="-21020" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -254,12 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>trail</t>
   </si>
   <si>
@@ -287,9 +281,6 @@
     <t>XL</t>
   </si>
   <si>
-    <t>euro</t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -402,9 +393,6 @@
   </si>
   <si>
     <t>https://bikeinsights.com/bikes/5fb779ff6865f3001759b27a-lapierre-crosshill?version=2023</t>
-  </si>
-  <si>
-    <t>a8:g43</t>
   </si>
   <si>
     <r>
@@ -534,6 +522,12 @@
       </rPr>
       <t>cm</t>
     </r>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>a8:g41</t>
   </si>
 </sst>
 </file>
@@ -939,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -950,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -958,7 +952,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,7 +976,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -990,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -998,25 +992,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1024,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C9" s="9">
         <v>517</v>
@@ -1047,7 +1041,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C10" s="9">
         <v>366</v>
@@ -1067,10 +1061,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" s="9">
         <v>1.41</v>
@@ -1093,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C12" s="9">
         <v>420</v>
@@ -1116,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" s="9">
         <v>525</v>
@@ -1136,10 +1130,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" s="9">
         <v>13.3</v>
@@ -1162,7 +1156,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" s="9">
         <v>70</v>
@@ -1185,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C16" s="9">
         <v>73</v>
@@ -1208,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9">
         <v>90</v>
@@ -1231,7 +1225,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18">
         <v>75</v>
@@ -1251,10 +1245,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C19" s="6">
         <v>273</v>
@@ -1277,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20" s="6">
         <v>435</v>
@@ -1297,10 +1291,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C21" s="6">
         <v>428.5</v>
@@ -1320,10 +1314,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="6">
         <v>579.6</v>
@@ -1343,10 +1337,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C23" s="6">
         <v>574.79999999999995</v>
@@ -1369,7 +1363,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C24" s="6">
         <v>1003.3</v>
@@ -1392,7 +1386,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C25" s="6">
         <v>45</v>
@@ -1415,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C26" s="6">
         <v>397</v>
@@ -1435,10 +1429,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C27" s="6">
         <v>78.8</v>
@@ -1458,10 +1452,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C28" s="6">
         <v>74</v>
@@ -1481,10 +1475,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C29" s="6">
         <v>25.3</v>
@@ -1507,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C30" s="6">
         <v>170</v>
@@ -1527,10 +1521,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C31" s="6">
         <v>61.6</v>
@@ -1550,10 +1544,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C32" s="6">
         <v>103</v>
@@ -1687,25 +1681,20 @@
       <c r="B40" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="3">
-        <f>C42</f>
+      <c r="C40">
         <v>155</v>
       </c>
-      <c r="D40" s="3">
-        <f>AVERAGE(D42,C43)</f>
-        <v>161</v>
-      </c>
-      <c r="E40" s="3">
-        <f t="shared" ref="E40:G40" si="0">AVERAGE(E42,D43)</f>
-        <v>171</v>
-      </c>
-      <c r="F40" s="3">
-        <f t="shared" si="0"/>
-        <v>181</v>
-      </c>
-      <c r="G40" s="3">
-        <f t="shared" si="0"/>
-        <v>189</v>
+      <c r="D40">
+        <v>160</v>
+      </c>
+      <c r="E40">
+        <v>170</v>
+      </c>
+      <c r="F40">
+        <v>180</v>
+      </c>
+      <c r="G40">
+        <v>188</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -1717,373 +1706,328 @@
       <c r="B41" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="3">
-        <f>D40</f>
-        <v>161</v>
-      </c>
-      <c r="D41" s="3">
-        <f t="shared" ref="D41:F41" si="1">E40</f>
-        <v>171</v>
-      </c>
-      <c r="E41" s="3">
-        <f t="shared" si="1"/>
-        <v>181</v>
-      </c>
-      <c r="F41" s="3">
-        <f t="shared" si="1"/>
-        <v>189</v>
-      </c>
-      <c r="G41" s="3">
-        <f t="shared" ref="D40:G41" si="2">G43</f>
+      <c r="C41">
+        <v>162</v>
+      </c>
+      <c r="D41">
+        <v>172</v>
+      </c>
+      <c r="E41">
+        <v>182</v>
+      </c>
+      <c r="F41">
+        <v>190</v>
+      </c>
+      <c r="G41">
         <v>196</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42">
-        <v>155</v>
-      </c>
-      <c r="D42">
-        <v>160</v>
-      </c>
-      <c r="E42">
-        <v>170</v>
-      </c>
-      <c r="F42">
-        <v>180</v>
-      </c>
-      <c r="G42">
-        <v>188</v>
-      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43">
-        <v>162</v>
-      </c>
-      <c r="D43">
-        <v>172</v>
-      </c>
-      <c r="E43">
-        <v>182</v>
-      </c>
-      <c r="F43">
-        <v>190</v>
-      </c>
-      <c r="G43">
-        <v>196</v>
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="A44" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="C45" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>127</v>
-      </c>
       <c r="E45" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>132</v>
+        <v>31</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" t="s">
-        <v>71</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>31</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="B50">
+        <v>45</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="B56">
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B57">
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58">
-        <v>142</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59">
-        <v>100</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B60">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62">
-        <v>27.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>50</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>85</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B69" s="1"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>52</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>53</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>55</v>
-      </c>
-      <c r="B73">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>56</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>58</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B76" s="1"/>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>60</v>
-      </c>
-      <c r="B78" s="1"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>61</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="B79">
+        <v>2799</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>62</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B80" s="1"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81">
-        <v>2799</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>64</v>
-      </c>
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
         <v>65</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>84</v>
+      <c r="B81" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Lapierre Crosshill 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C82DF8-7DEF-2540-AF0F-D3043E43AF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BEA3C1-697C-4B4E-AD80-B2963CCAA5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28100" yWindow="-21020" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -261,9 +261,6 @@
   </si>
   <si>
     <t>Lapierre</t>
-  </si>
-  <si>
-    <t>https://www.lapierrebikes.com/nl-en/v/bikes/?attrModelYears=2025&amp;attrProductLine=Crosshill%20CF</t>
   </si>
   <si>
     <t>XS</t>
@@ -528,6 +525,12 @@
   </si>
   <si>
     <t>a8:g41</t>
+  </si>
+  <si>
+    <t>https://www.lapierrebikes.com/nl-en/crosshill/</t>
+  </si>
+  <si>
+    <t>https://adfnjoxprq.cloudimg.io/v7/_lapierre_prod/media/1d/5c/a0/1702047311/Crosshill%205.0%20-%20Lapierre%20MY24%20-%20Cover.png</t>
   </si>
 </sst>
 </file>
@@ -952,7 +955,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -976,7 +979,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -984,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -992,25 +1000,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1018,7 +1026,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="9">
         <v>517</v>
@@ -1041,7 +1049,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="9">
         <v>366</v>
@@ -1061,10 +1069,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="9">
         <v>1.41</v>
@@ -1087,7 +1095,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="9">
         <v>420</v>
@@ -1110,7 +1118,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9">
         <v>525</v>
@@ -1130,10 +1138,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="9">
         <v>13.3</v>
@@ -1156,7 +1164,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="9">
         <v>70</v>
@@ -1179,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9">
         <v>73</v>
@@ -1202,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="9">
         <v>90</v>
@@ -1225,7 +1233,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18">
         <v>75</v>
@@ -1245,10 +1253,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="6">
         <v>273</v>
@@ -1271,7 +1279,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="6">
         <v>435</v>
@@ -1291,10 +1299,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="6">
         <v>428.5</v>
@@ -1317,7 +1325,7 @@
         <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6">
         <v>579.6</v>
@@ -1337,10 +1345,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="6">
         <v>574.79999999999995</v>
@@ -1363,7 +1371,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C24" s="6">
         <v>1003.3</v>
@@ -1386,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" s="6">
         <v>45</v>
@@ -1409,7 +1417,7 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="6">
         <v>397</v>
@@ -1432,7 +1440,7 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="6">
         <v>78.8</v>
@@ -1452,10 +1460,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C28" s="6">
         <v>74</v>
@@ -1475,10 +1483,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C29" s="6">
         <v>25.3</v>
@@ -1501,7 +1509,7 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C30" s="6">
         <v>170</v>
@@ -1521,10 +1529,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="6">
         <v>61.6</v>
@@ -1544,10 +1552,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="6">
         <v>103</v>
@@ -1739,19 +1747,19 @@
         <v>30</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1762,19 +1770,19 @@
         <v>67</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1785,16 +1793,16 @@
         <v>69</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1810,7 +1818,7 @@
         <v>31</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1931,7 +1939,7 @@
         <v>51</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2027,7 +2035,7 @@
         <v>65</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Lapierre Crosshill 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BEA3C1-697C-4B4E-AD80-B2963CCAA5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2B8993-B3AA-0243-B2DF-3538423ACE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28100" yWindow="-21020" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11060" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -531,6 +531,12 @@
   </si>
   <si>
     <t>https://adfnjoxprq.cloudimg.io/v7/_lapierre_prod/media/1d/5c/a0/1702047311/Crosshill%205.0%20-%20Lapierre%20MY24%20-%20Cover.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dijon, France</t>
   </si>
 </sst>
 </file>
@@ -936,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2038,6 +2044,14 @@
         <v>129</v>
       </c>
     </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Lapierre Crosshill 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2B8993-B3AA-0243-B2DF-3538423ACE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D6581B-4BCA-3B41-B771-B5C6184956B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11060" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -1952,7 +1952,9 @@
       <c r="A68" t="s">
         <v>52</v>
       </c>
-      <c r="B68" s="1"/>
+      <c r="B68" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">

--- a/data/gravel/Lapierre Crosshill 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D6581B-4BCA-3B41-B771-B5C6184956B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBBBBE9-1E21-E744-BC14-7CF711228878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="141">
   <si>
     <t>brand</t>
   </si>
@@ -537,6 +537,24 @@
   </si>
   <si>
     <t>Dijon, France</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -942,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1890,167 +1908,197 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>135</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60">
-        <v>27.2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B66">
+        <v>27.2</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>55</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>56</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>58</v>
-      </c>
-      <c r="B74" s="1">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>60</v>
-      </c>
-      <c r="B76" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>61</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79">
-        <v>2799</v>
+        <v>57</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>64</v>
-      </c>
-      <c r="B80" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B81" s="1"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
+        <v>60</v>
+      </c>
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>63</v>
+      </c>
+      <c r="B85">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>65</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
         <v>133</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B88" t="s">
         <v>134</v>
       </c>
     </row>
